--- a/docs/webbrain-mode-tier-tool-chart.xlsx
+++ b/docs/webbrain-mode-tier-tool-chart.xlsx
@@ -1379,11 +1379,11 @@
       <x:c r="C43" s="51" t="str">
         <x:v>No</x:v>
       </x:c>
-      <x:c r="D43" s="53" t="str">
-        <x:v>Chrome</x:v>
-      </x:c>
-      <x:c r="E43" s="53" t="str">
-        <x:v>Chrome</x:v>
+      <x:c r="D43" s="49" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E43" s="49" t="str">
+        <x:v>Yes</x:v>
       </x:c>
       <x:c r="F43" s="50" t="str">
         <x:v>No</x:v>

--- a/docs/webbrain-mode-tier-tool-chart.xlsx
+++ b/docs/webbrain-mode-tier-tool-chart.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Chart" sheetId="1" r:id="R300a5b2f4b574465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tool Chart" sheetId="1" r:id="R4a29cae962224db0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,7 +13,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -59,8 +59,13 @@
       <x:color rgb="FF744210"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B7280"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="12">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -97,6 +102,26 @@
         <x:fgColor rgb="FFFFF8E5"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8F1FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF0D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFDFF3E4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF3F4F6"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="10">
     <x:border/>
@@ -194,7 +219,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="57">
+  <x:cellXfs count="82">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -304,6 +329,81 @@
     <x:xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="8" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="10" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -312,8 +412,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ModeTierToolChart" displayName="ModeTierToolChart" ref="A1:F50" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F50"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="ModeTierToolChart" displayName="ModeTierToolChart" ref="A1:F51" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F51"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="Tool"/>
     <x:tableColumn id="2" name="Ask"/>
@@ -553,19 +653,19 @@
       <x:c r="A2" s="35" t="str">
         <x:v>get_accessibility_tree</x:v>
       </x:c>
-      <x:c r="B2" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C2" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D2" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E2" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F2" s="50" t="str">
+      <x:c r="B2" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C2" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D2" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E2" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F2" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -573,19 +673,19 @@
       <x:c r="A3" s="35" t="str">
         <x:v>read_page</x:v>
       </x:c>
-      <x:c r="B3" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C3" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D3" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E3" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F3" s="50" t="str">
+      <x:c r="B3" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C3" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D3" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E3" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F3" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -593,19 +693,19 @@
       <x:c r="A4" s="35" t="str">
         <x:v>read_pdf</x:v>
       </x:c>
-      <x:c r="B4" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C4" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D4" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E4" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F4" s="50" t="str">
+      <x:c r="B4" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C4" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D4" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E4" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F4" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -613,19 +713,19 @@
       <x:c r="A5" s="35" t="str">
         <x:v>read_page_source</x:v>
       </x:c>
-      <x:c r="B5" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C5" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D5" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E5" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="F5" s="52" t="str">
+      <x:c r="B5" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C5" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D5" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E5" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F5" s="64" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -633,19 +733,19 @@
       <x:c r="A6" s="35" t="str">
         <x:v>get_window_info</x:v>
       </x:c>
-      <x:c r="B6" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C6" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D6" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E6" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F6" s="50" t="str">
+      <x:c r="B6" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C6" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D6" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E6" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F6" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -653,19 +753,19 @@
       <x:c r="A7" s="35" t="str">
         <x:v>get_interactive_elements</x:v>
       </x:c>
-      <x:c r="B7" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C7" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D7" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E7" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F7" s="50" t="str">
+      <x:c r="B7" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C7" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D7" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E7" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F7" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -673,19 +773,19 @@
       <x:c r="A8" s="35" t="str">
         <x:v>scroll</x:v>
       </x:c>
-      <x:c r="B8" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C8" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D8" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E8" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F8" s="50" t="str">
+      <x:c r="B8" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C8" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D8" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E8" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F8" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -693,19 +793,19 @@
       <x:c r="A9" s="35" t="str">
         <x:v>extract_data</x:v>
       </x:c>
-      <x:c r="B9" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C9" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D9" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E9" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F9" s="50" t="str">
+      <x:c r="B9" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C9" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D9" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E9" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F9" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -713,19 +813,19 @@
       <x:c r="A10" s="35" t="str">
         <x:v>inspect_element_styles</x:v>
       </x:c>
-      <x:c r="B10" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C10" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D10" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E10" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="F10" s="52" t="str">
+      <x:c r="B10" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C10" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D10" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E10" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F10" s="64" t="str">
         <x:v>Yes</x:v>
       </x:c>
     </x:row>
@@ -733,19 +833,19 @@
       <x:c r="A11" s="35" t="str">
         <x:v>wait_for_stable</x:v>
       </x:c>
-      <x:c r="B11" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C11" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D11" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E11" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F11" s="50" t="str">
+      <x:c r="B11" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C11" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D11" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E11" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F11" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -753,19 +853,19 @@
       <x:c r="A12" s="35" t="str">
         <x:v>get_selection</x:v>
       </x:c>
-      <x:c r="B12" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C12" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D12" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E12" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F12" s="50" t="str">
+      <x:c r="B12" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C12" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D12" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E12" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F12" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -773,19 +873,19 @@
       <x:c r="A13" s="35" t="str">
         <x:v>done</x:v>
       </x:c>
-      <x:c r="B13" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C13" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D13" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E13" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F13" s="50" t="str">
+      <x:c r="B13" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C13" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D13" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E13" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F13" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -793,19 +893,19 @@
       <x:c r="A14" s="35" t="str">
         <x:v>clarify</x:v>
       </x:c>
-      <x:c r="B14" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C14" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D14" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E14" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F14" s="50" t="str">
+      <x:c r="B14" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C14" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D14" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E14" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F14" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -813,19 +913,19 @@
       <x:c r="A15" s="35" t="str">
         <x:v>fetch_url</x:v>
       </x:c>
-      <x:c r="B15" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C15" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D15" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E15" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F15" s="50" t="str">
+      <x:c r="B15" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C15" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D15" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E15" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F15" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -833,19 +933,19 @@
       <x:c r="A16" s="35" t="str">
         <x:v>research_url</x:v>
       </x:c>
-      <x:c r="B16" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C16" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D16" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E16" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F16" s="50" t="str">
+      <x:c r="B16" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C16" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D16" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E16" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F16" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -853,19 +953,19 @@
       <x:c r="A17" s="35" t="str">
         <x:v>list_downloads</x:v>
       </x:c>
-      <x:c r="B17" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="C17" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D17" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E17" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F17" s="50" t="str">
+      <x:c r="B17" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="C17" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D17" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E17" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F17" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -873,19 +973,19 @@
       <x:c r="A18" s="35" t="str">
         <x:v>click_ax</x:v>
       </x:c>
-      <x:c r="B18" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C18" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D18" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E18" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F18" s="50" t="str">
+      <x:c r="B18" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C18" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D18" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E18" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F18" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -893,19 +993,19 @@
       <x:c r="A19" s="35" t="str">
         <x:v>type_ax</x:v>
       </x:c>
-      <x:c r="B19" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C19" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D19" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E19" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F19" s="50" t="str">
+      <x:c r="B19" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C19" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D19" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E19" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F19" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -913,19 +1013,19 @@
       <x:c r="A20" s="35" t="str">
         <x:v>set_field</x:v>
       </x:c>
-      <x:c r="B20" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C20" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D20" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E20" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F20" s="50" t="str">
+      <x:c r="B20" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C20" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D20" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E20" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F20" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -933,19 +1033,19 @@
       <x:c r="A21" s="35" t="str">
         <x:v>resize_window</x:v>
       </x:c>
-      <x:c r="B21" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C21" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D21" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E21" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F21" s="50" t="str">
+      <x:c r="B21" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C21" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D21" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E21" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F21" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -953,19 +1053,19 @@
       <x:c r="A22" s="35" t="str">
         <x:v>click</x:v>
       </x:c>
-      <x:c r="B22" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C22" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D22" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E22" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F22" s="50" t="str">
+      <x:c r="B22" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C22" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D22" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E22" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F22" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -973,19 +1073,19 @@
       <x:c r="A23" s="35" t="str">
         <x:v>type_text</x:v>
       </x:c>
-      <x:c r="B23" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C23" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D23" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E23" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F23" s="50" t="str">
+      <x:c r="B23" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C23" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D23" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E23" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F23" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -993,19 +1093,19 @@
       <x:c r="A24" s="35" t="str">
         <x:v>press_keys</x:v>
       </x:c>
-      <x:c r="B24" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C24" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D24" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E24" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F24" s="50" t="str">
+      <x:c r="B24" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C24" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D24" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E24" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F24" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -1013,19 +1113,19 @@
       <x:c r="A25" s="35" t="str">
         <x:v>navigate</x:v>
       </x:c>
-      <x:c r="B25" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C25" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D25" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E25" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F25" s="50" t="str">
+      <x:c r="B25" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C25" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D25" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E25" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F25" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -1033,19 +1133,19 @@
       <x:c r="A26" s="35" t="str">
         <x:v>wait_for_element</x:v>
       </x:c>
-      <x:c r="B26" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C26" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D26" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E26" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F26" s="50" t="str">
+      <x:c r="B26" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C26" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D26" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E26" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F26" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
@@ -1053,489 +1153,501 @@
       <x:c r="A27" s="35" t="str">
         <x:v>new_tab</x:v>
       </x:c>
-      <x:c r="B27" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C27" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D27" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E27" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F27" s="50" t="str">
+      <x:c r="B27" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C27" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D27" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E27" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F27" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="35" t="str">
-        <x:v>scratchpad_write</x:v>
-      </x:c>
-      <x:c r="B28" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C28" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D28" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E28" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F28" s="50" t="str">
+        <x:v>promote_iframe</x:v>
+      </x:c>
+      <x:c r="B28" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C28" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D28" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E28" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F28" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="22" customHeight="1">
       <x:c r="A29" s="35" t="str">
-        <x:v>progress_update</x:v>
-      </x:c>
-      <x:c r="B29" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C29" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D29" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E29" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F29" s="50" t="str">
+        <x:v>scratchpad_write</x:v>
+      </x:c>
+      <x:c r="B29" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C29" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D29" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E29" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F29" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
       <x:c r="A30" s="35" t="str">
-        <x:v>progress_read</x:v>
-      </x:c>
-      <x:c r="B30" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C30" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="D30" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E30" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F30" s="50" t="str">
+        <x:v>progress_update</x:v>
+      </x:c>
+      <x:c r="B30" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C30" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D30" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E30" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F30" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="22" customHeight="1">
       <x:c r="A31" s="35" t="str">
-        <x:v>download_social_media</x:v>
-      </x:c>
-      <x:c r="B31" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C31" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D31" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E31" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F31" s="50" t="str">
+        <x:v>progress_read</x:v>
+      </x:c>
+      <x:c r="B31" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C31" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="D31" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E31" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F31" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
       <x:c r="A32" s="35" t="str">
-        <x:v>solve_captcha</x:v>
-      </x:c>
-      <x:c r="B32" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C32" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D32" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E32" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F32" s="50" t="str">
+        <x:v>download_social_media</x:v>
+      </x:c>
+      <x:c r="B32" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C32" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D32" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E32" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F32" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="22" customHeight="1">
       <x:c r="A33" s="35" t="str">
-        <x:v>go_back</x:v>
-      </x:c>
-      <x:c r="B33" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C33" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D33" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E33" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F33" s="50" t="str">
+        <x:v>solve_captcha</x:v>
+      </x:c>
+      <x:c r="B33" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C33" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D33" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E33" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F33" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
       <x:c r="A34" s="35" t="str">
-        <x:v>go_forward</x:v>
-      </x:c>
-      <x:c r="B34" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C34" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D34" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E34" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F34" s="50" t="str">
+        <x:v>go_back</x:v>
+      </x:c>
+      <x:c r="B34" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C34" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D34" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E34" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F34" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="22" customHeight="1">
       <x:c r="A35" s="35" t="str">
-        <x:v>schedule_resume</x:v>
-      </x:c>
-      <x:c r="B35" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C35" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D35" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E35" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F35" s="50" t="str">
+        <x:v>go_forward</x:v>
+      </x:c>
+      <x:c r="B35" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C35" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D35" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E35" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F35" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="35" t="str">
-        <x:v>schedule_task</x:v>
-      </x:c>
-      <x:c r="B36" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C36" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D36" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E36" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F36" s="50" t="str">
+        <x:v>schedule_resume</x:v>
+      </x:c>
+      <x:c r="B36" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C36" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D36" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E36" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F36" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="22" customHeight="1">
       <x:c r="A37" s="35" t="str">
-        <x:v>iframe_read</x:v>
-      </x:c>
-      <x:c r="B37" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C37" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D37" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E37" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F37" s="50" t="str">
+        <x:v>schedule_task</x:v>
+      </x:c>
+      <x:c r="B37" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C37" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D37" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E37" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F37" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="22" customHeight="1">
       <x:c r="A38" s="35" t="str">
-        <x:v>iframe_click</x:v>
-      </x:c>
-      <x:c r="B38" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C38" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D38" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E38" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F38" s="50" t="str">
+        <x:v>iframe_read</x:v>
+      </x:c>
+      <x:c r="B38" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C38" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D38" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E38" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F38" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="22" customHeight="1">
       <x:c r="A39" s="35" t="str">
-        <x:v>iframe_type</x:v>
-      </x:c>
-      <x:c r="B39" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C39" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D39" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E39" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F39" s="50" t="str">
+        <x:v>iframe_click</x:v>
+      </x:c>
+      <x:c r="B39" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C39" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D39" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E39" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F39" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="22" customHeight="1">
       <x:c r="A40" s="35" t="str">
-        <x:v>read_downloaded_file</x:v>
-      </x:c>
-      <x:c r="B40" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C40" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D40" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E40" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F40" s="50" t="str">
+        <x:v>iframe_type</x:v>
+      </x:c>
+      <x:c r="B40" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C40" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D40" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E40" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F40" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="22" customHeight="1">
       <x:c r="A41" s="35" t="str">
-        <x:v>download_files</x:v>
-      </x:c>
-      <x:c r="B41" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C41" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D41" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E41" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F41" s="50" t="str">
+        <x:v>read_downloaded_file</x:v>
+      </x:c>
+      <x:c r="B41" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C41" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D41" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E41" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F41" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="22" customHeight="1">
       <x:c r="A42" s="35" t="str">
-        <x:v>download_resource_from_page</x:v>
-      </x:c>
-      <x:c r="B42" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C42" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D42" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E42" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F42" s="50" t="str">
+        <x:v>download_files</x:v>
+      </x:c>
+      <x:c r="B42" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C42" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D42" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E42" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F42" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="22" customHeight="1">
       <x:c r="A43" s="35" t="str">
-        <x:v>upload_file</x:v>
-      </x:c>
-      <x:c r="B43" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C43" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D43" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E43" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F43" s="50" t="str">
+        <x:v>download_resource_from_page</x:v>
+      </x:c>
+      <x:c r="B43" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C43" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D43" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E43" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F43" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="22" customHeight="1">
       <x:c r="A44" s="35" t="str">
-        <x:v>verify_form</x:v>
-      </x:c>
-      <x:c r="B44" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C44" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D44" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="E44" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F44" s="50" t="str">
+        <x:v>upload_file</x:v>
+      </x:c>
+      <x:c r="B44" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C44" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D44" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E44" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F44" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="22" customHeight="1">
       <x:c r="A45" s="35" t="str">
-        <x:v>hover</x:v>
-      </x:c>
-      <x:c r="B45" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C45" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D45" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E45" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F45" s="50" t="str">
+        <x:v>verify_form</x:v>
+      </x:c>
+      <x:c r="B45" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C45" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D45" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="E45" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F45" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="22" customHeight="1">
       <x:c r="A46" s="35" t="str">
-        <x:v>drag_drop</x:v>
-      </x:c>
-      <x:c r="B46" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C46" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D46" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E46" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F46" s="50" t="str">
+        <x:v>hover</x:v>
+      </x:c>
+      <x:c r="B46" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C46" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D46" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E46" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F46" s="73" t="str">
         <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="22" customHeight="1">
       <x:c r="A47" s="35" t="str">
-        <x:v>get_shadow_dom</x:v>
-      </x:c>
-      <x:c r="B47" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C47" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D47" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E47" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F47" s="52" t="str">
-        <x:v>Yes</x:v>
+        <x:v>drag_drop</x:v>
+      </x:c>
+      <x:c r="B47" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C47" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D47" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E47" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F47" s="73" t="str">
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="22" customHeight="1">
       <x:c r="A48" s="35" t="str">
-        <x:v>shadow_dom_query</x:v>
-      </x:c>
-      <x:c r="B48" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C48" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D48" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E48" s="53" t="str">
-        <x:v>Chrome</x:v>
-      </x:c>
-      <x:c r="F48" s="54" t="str">
-        <x:v>Chrome</x:v>
+        <x:v>get_shadow_dom</x:v>
+      </x:c>
+      <x:c r="B48" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C48" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D48" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E48" s="63" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F48" s="64" t="str">
+        <x:v>Yes</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="22" customHeight="1">
       <x:c r="A49" s="35" t="str">
-        <x:v>get_frames</x:v>
-      </x:c>
-      <x:c r="B49" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C49" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D49" s="51" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E49" s="49" t="str">
-        <x:v>Yes</x:v>
-      </x:c>
-      <x:c r="F49" s="52" t="str">
-        <x:v>Yes</x:v>
+        <x:v>shadow_dom_query</x:v>
+      </x:c>
+      <x:c r="B49" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C49" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D49" s="75" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E49" s="58" t="str">
+        <x:v>Chrome</x:v>
+      </x:c>
+      <x:c r="F49" s="60" t="str">
+        <x:v>Chrome</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="22" customHeight="1">
       <x:c r="A50" s="42" t="str">
+        <x:v>get_frames</x:v>
+      </x:c>
+      <x:c r="B50" s="79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C50" s="79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D50" s="79" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E50" s="69" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F50" s="71" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="45" t="str">
         <x:v>execute_js</x:v>
       </x:c>
-      <x:c r="B50" s="55" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="C50" s="55" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="D50" s="55" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E50" s="55" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="F50" s="56" t="str">
+      <x:c r="B51" s="81" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="C51" s="81" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="D51" s="81" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E51" s="81" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="F51" s="62" t="str">
         <x:v>Firefox</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="45"/>
-      <x:c r="B51" s="45"/>
-      <x:c r="C51" s="45"/>
-      <x:c r="D51" s="45"/>
-      <x:c r="E51" s="45"/>
-      <x:c r="F51" s="45"/>
     </x:row>
     <x:row r="52" ht="30" customHeight="1">
       <x:c r="A52" s="46" t="str">
@@ -1563,7 +1675,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff2687632b0e4f3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10838b3d981943ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>